--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-02-2026.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /40mm_celotex_tb4000_pir_insulation.html (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
+          <t>£16.05</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£15.99</t>
+          <t>£15.98</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£27.43</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£745.00</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-xr4165-165mm-x-2-4m-x-1-2m-pallet-of-12 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>£61.03</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>£1163.76</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
